--- a/data/trans_camb/IP18A01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 12,42</t>
+          <t>1,3; 12,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 12,32</t>
+          <t>1,15; 11,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 22,11</t>
+          <t>-3,99; 24,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 10,77</t>
+          <t>0,53; 11,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 9,84</t>
+          <t>-0,04; 10,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,07; -2,44</t>
+          <t>-8,46; -2,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 9,74</t>
+          <t>2,28; 9,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 8,82</t>
+          <t>1,57; 8,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 7,67</t>
+          <t>-4,48; 8,68</t>
         </is>
       </c>
     </row>
@@ -783,27 +783,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,51; 587,78</t>
+          <t>12,09; 603,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 588,61</t>
+          <t>3,68; 577,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1138,49</t>
+          <t>-100,0; 1389,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 382,76</t>
+          <t>1,53; 450,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 341,86</t>
+          <t>-4,55; 486,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,7; 319,37</t>
+          <t>27,87; 322,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,45; 304,83</t>
+          <t>26,83; 302,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 259,2</t>
+          <t>-100,0; 327,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 3,97</t>
+          <t>-3,96; 4,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 4,93</t>
+          <t>-3,26; 5,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 13,14</t>
+          <t>-4,33; 11,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 7,6</t>
+          <t>-1,51; 7,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 7,27</t>
+          <t>-0,95; 7,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 9,64</t>
+          <t>-3,36; 9,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 4,84</t>
+          <t>-1,31; 4,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,88</t>
+          <t>-1,46; 4,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 7,32</t>
+          <t>-2,92; 7,23</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,67; 84,94</t>
+          <t>-45,8; 90,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,13; 101,94</t>
+          <t>-38,64; 111,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,95; 287,98</t>
+          <t>-61,36; 199,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 186,84</t>
+          <t>-23,87; 176,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 183,73</t>
+          <t>-14,73; 190,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,4; 231,16</t>
+          <t>-56,0; 222,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 106,35</t>
+          <t>-17,3; 95,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 106,81</t>
+          <t>-18,52; 94,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,79; 138,43</t>
+          <t>-42,48; 139,45</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 3,51</t>
+          <t>-8,03; 3,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 4,04</t>
+          <t>-7,43; 4,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 5,94</t>
+          <t>-12,47; 4,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 4,89</t>
+          <t>-6,21; 4,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 3,74</t>
+          <t>-6,55; 4,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,61; -4,06</t>
+          <t>-13,32; -3,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 2,73</t>
+          <t>-5,16; 2,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 2,17</t>
+          <t>-5,76; 2,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,15; -2,55</t>
+          <t>-11,57; -2,34</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-55,35; 49,67</t>
+          <t>-57,48; 47,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,51; 55,12</t>
+          <t>-54,57; 66,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 86,44</t>
+          <t>-100,0; 104,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 73,66</t>
+          <t>-49,05; 63,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,68; 58,8</t>
+          <t>-54,34; 62,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -25,34</t>
+          <t>-100,0; -11,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 36,15</t>
+          <t>-44,69; 38,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-44,65; 30,37</t>
+          <t>-45,57; 27,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-94,0; -15,69</t>
+          <t>-93,75; -10,82</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 6,66</t>
+          <t>-4,14; 6,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 5,26</t>
+          <t>-6,15; 5,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 9,78</t>
+          <t>-10,66; 10,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 4,42</t>
+          <t>-6,29; 4,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 1,71</t>
+          <t>-8,83; 1,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 1,76</t>
+          <t>-13,94; 1,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 4,44</t>
+          <t>-3,72; 4,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 2,19</t>
+          <t>-5,67; 1,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 1,2</t>
+          <t>-10,61; 1,12</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,44; 70,74</t>
+          <t>-30,73; 79,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,18; 63,35</t>
+          <t>-43,07; 61,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,14; 114,97</t>
+          <t>-82,3; 109,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 46,49</t>
+          <t>-40,56; 47,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,75; 21,04</t>
+          <t>-58,41; 22,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,37</t>
+          <t>-100,0; 38,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 44,28</t>
+          <t>-25,77; 41,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,5; 23,23</t>
+          <t>-42,27; 19,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-81,54; 14,63</t>
+          <t>-81,51; 12,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 4,01</t>
+          <t>-1,38; 3,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,36</t>
+          <t>-1,61; 3,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 4,38</t>
+          <t>-5,31; 4,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 4,23</t>
+          <t>-1,1; 4,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 3,14</t>
+          <t>-2,17; 2,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -0,85</t>
+          <t>-7,22; -0,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,17</t>
+          <t>-0,5; 3,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,46</t>
+          <t>-1,21; 2,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,16</t>
+          <t>-5,37; -0,09</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 56,93</t>
+          <t>-13,44; 54,28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 47,06</t>
+          <t>-16,57; 49,71</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 57,88</t>
+          <t>-58,42; 55,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 60,79</t>
+          <t>-11,48; 57,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 44,36</t>
+          <t>-22,69; 38,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-76,14; -5,88</t>
+          <t>-76,76; -7,47</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 41,77</t>
+          <t>-5,42; 41,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 31,83</t>
+          <t>-13,4; 34,81</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-59,14; -1,87</t>
+          <t>-59,39; -0,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 12,15</t>
+          <t>0,86; 11,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 11,69</t>
+          <t>0,89; 12,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 24,47</t>
+          <t>-4,58; 21,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 11,18</t>
+          <t>0,38; 11,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 10,42</t>
+          <t>-0,02; 10,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,46; -2,24</t>
+          <t>-8,3; -2,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 9,61</t>
+          <t>2,39; 9,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,78</t>
+          <t>1,66; 9,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 8,68</t>
+          <t>-4,7; 8,81</t>
         </is>
       </c>
     </row>
@@ -783,27 +783,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,09; 603,66</t>
+          <t>2,63; 493,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 577,24</t>
+          <t>1,35; 601,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1389,29</t>
+          <t>-100,0; 957,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 450,2</t>
+          <t>-0,62; 411,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 486,18</t>
+          <t>-11,65; 369,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,87; 322,35</t>
+          <t>33,24; 332,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,83; 302,99</t>
+          <t>25,22; 326,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 327,7</t>
+          <t>-100,0; 273,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 4,34</t>
+          <t>-4,43; 3,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 5,01</t>
+          <t>-2,94; 5,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 11,81</t>
+          <t>-4,8; 12,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 7,47</t>
+          <t>-1,03; 7,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 7,2</t>
+          <t>-1,16; 7,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 9,5</t>
+          <t>-3,27; 9,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,46</t>
+          <t>-1,25; 4,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,76</t>
+          <t>-0,93; 4,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 7,23</t>
+          <t>-2,86; 7,24</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,8; 90,21</t>
+          <t>-50,19; 76,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 111,0</t>
+          <t>-34,64; 130,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,36; 199,69</t>
+          <t>-64,19; 281,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 176,01</t>
+          <t>-17,09; 199,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 190,97</t>
+          <t>-21,17; 188,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,0; 222,93</t>
+          <t>-49,23; 206,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 95,4</t>
+          <t>-16,63; 95,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 94,4</t>
+          <t>-13,71; 101,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,48; 139,45</t>
+          <t>-40,85; 139,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 3,54</t>
+          <t>-7,64; 3,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 4,52</t>
+          <t>-7,41; 4,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 4,26</t>
+          <t>-11,81; 5,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 4,78</t>
+          <t>-6,12; 4,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 4,38</t>
+          <t>-7,53; 3,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,32; -3,81</t>
+          <t>-13,48; -4,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 2,91</t>
+          <t>-5,17; 2,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 2,21</t>
+          <t>-5,73; 2,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,57; -2,34</t>
+          <t>-11,54; -2,58</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-57,48; 47,45</t>
+          <t>-55,97; 44,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,57; 66,59</t>
+          <t>-54,3; 50,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 104,9</t>
+          <t>-100,0; 72,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,05; 63,18</t>
+          <t>-48,27; 67,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,34; 62,01</t>
+          <t>-60,63; 60,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -11,73</t>
+          <t>-100,0; -16,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,69; 38,19</t>
+          <t>-43,25; 30,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-45,57; 27,91</t>
+          <t>-45,68; 27,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-93,75; -10,82</t>
+          <t>-94,15; -14,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 6,96</t>
+          <t>-4,27; 7,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 5,6</t>
+          <t>-6,17; 5,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 10,74</t>
+          <t>-10,65; 10,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 4,58</t>
+          <t>-5,8; 5,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 1,88</t>
+          <t>-8,81; 1,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 1,53</t>
+          <t>-13,61; 0,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 4,23</t>
+          <t>-3,92; 4,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 1,9</t>
+          <t>-5,57; 1,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 1,12</t>
+          <t>-10,59; 1,53</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,73; 79,07</t>
+          <t>-31,4; 79,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 61,68</t>
+          <t>-44,01; 63,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-82,3; 109,77</t>
+          <t>-81,21; 128,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,56; 47,73</t>
+          <t>-39,99; 52,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,41; 22,01</t>
+          <t>-57,72; 19,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 38,46</t>
+          <t>-100,0; 23,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 41,65</t>
+          <t>-27,55; 42,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,27; 19,08</t>
+          <t>-41,03; 20,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-81,51; 12,92</t>
+          <t>-79,69; 21,27</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,93</t>
+          <t>-1,71; 3,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,65</t>
+          <t>-1,83; 3,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,05</t>
+          <t>-5,33; 4,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,17</t>
+          <t>-0,77; 4,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,64</t>
+          <t>-2,19; 2,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -0,77</t>
+          <t>-7,16; -0,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,23</t>
+          <t>-0,44; 3,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,55</t>
+          <t>-1,1; 2,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,37; -0,09</t>
+          <t>-5,48; -0,09</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 54,28</t>
+          <t>-16,84; 49,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 49,71</t>
+          <t>-19,13; 50,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 55,26</t>
+          <t>-58,45; 60,39</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 57,1</t>
+          <t>-8,2; 63,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 38,09</t>
+          <t>-23,21; 41,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-76,76; -7,47</t>
+          <t>-78,11; -10,5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 41,94</t>
+          <t>-4,39; 44,3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 34,81</t>
+          <t>-12,52; 30,19</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-59,39; -0,63</t>
+          <t>-61,35; -1,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores cuya última consulta médica fue por vacunación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,53</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,61</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-4,6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,49</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>6,01</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,53</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,61</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,6</t>
+          <t>3,48</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,0</t>
+          <t>-0,87</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 11,83</t>
+          <t>0,57; 10,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 12,18</t>
+          <t>-0,64; 9,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 21,89</t>
+          <t>-8,07; -2,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 11,07</t>
+          <t>1,87; 12,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 10,12</t>
+          <t>1,32; 12,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,3; -2,23</t>
+          <t>-3,92; 24,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 9,74</t>
+          <t>2,19; 9,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 9,36</t>
+          <t>1,51; 8,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 8,81</t>
+          <t>-4,6; 8,96</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>120,34%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>100,27%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>162,11%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>150,29%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>88,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>120,34%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,27%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-23,23%</t>
+          <t>-20,1%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 493,68</t>
+          <t>-3,87; 382,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 601,16</t>
+          <t>-17,9; 341,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 957,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 411,4</t>
+          <t>18,51; 587,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 369,77</t>
+          <t>3,83; 588,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1380,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,24; 332,38</t>
+          <t>31,7; 319,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,22; 326,32</t>
+          <t>22,45; 304,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 273,82</t>
+          <t>-100,0; 332,0</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,07</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,44</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,73</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,07</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 3,69</t>
+          <t>-1,25; 7,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 5,23</t>
+          <t>-1,24; 7,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 12,36</t>
+          <t>-3,89; 9,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 7,73</t>
+          <t>-3,81; 3,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 7,3</t>
+          <t>-3,73; 4,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 9,25</t>
+          <t>-4,55; 13,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,8</t>
+          <t>-1,34; 4,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 4,84</t>
+          <t>-1,15; 4,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 7,24</t>
+          <t>-2,59; 7,41</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>53,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>51,88%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24,86%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2,94%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>10,74%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19,03%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>53,25%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>51,88%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,19; 76,66</t>
+          <t>-19,96; 186,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,64; 130,25</t>
+          <t>-18,61; 183,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-64,19; 281,68</t>
+          <t>-61,81; 233,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,09; 199,97</t>
+          <t>-45,67; 84,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 188,47</t>
+          <t>-41,13; 101,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,23; 206,11</t>
+          <t>-59,58; 310,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 95,69</t>
+          <t>-17,48; 106,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 101,52</t>
+          <t>-16,37; 106,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,85; 139,25</t>
+          <t>-39,52; 131,3</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,89</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,71</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-8,92</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-2,03</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,6</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-6,02</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-8,66</t>
+          <t>-6,3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,49</t>
+          <t>-7,8</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 3,39</t>
+          <t>-6,29; 4,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 4,09</t>
+          <t>-7,83; 3,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 5,24</t>
+          <t>-13,79; -4,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 4,41</t>
+          <t>-7,96; 3,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 3,61</t>
+          <t>-8,04; 4,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,48; -4,01</t>
+          <t>-11,94; 5,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 2,44</t>
+          <t>-5,33; 2,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 2,15</t>
+          <t>-5,51; 2,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,54; -2,58</t>
+          <t>-11,4; -3,23</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-8,95%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-17,24%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-90,03%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-18,97%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-14,98%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-56,21%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-8,95%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-17,24%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-87,39%</t>
+          <t>-58,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-72,72%</t>
+          <t>-75,74%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-55,97; 44,0</t>
+          <t>-49,3; 73,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,3; 50,57</t>
+          <t>-58,68; 58,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 72,95</t>
+          <t>-100,0; -40,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,27; 67,83</t>
+          <t>-55,35; 49,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,63; 60,4</t>
+          <t>-55,51; 55,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -16,22</t>
+          <t>-100,0; 87,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,25; 30,16</t>
+          <t>-43,13; 36,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-45,68; 27,77</t>
+          <t>-44,65; 30,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-94,15; -14,1</t>
+          <t>-94,87; -22,21</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-8,72</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,22</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,17</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,64</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,31</t>
+          <t>-2,99</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,74</t>
+          <t>-5,77</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 7,01</t>
+          <t>-6,23; 4,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 5,4</t>
+          <t>-8,77; 1,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 10,86</t>
+          <t>-13,35; 0,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 5,12</t>
+          <t>-4,31; 6,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 1,67</t>
+          <t>-6,14; 5,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 0,75</t>
+          <t>-10,64; 10,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 4,23</t>
+          <t>-3,54; 4,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 1,93</t>
+          <t>-5,23; 2,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 1,53</t>
+          <t>-10,68; 1,25</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-4,91%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-29,18%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-69,97%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>12,55%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-1,92%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-27,86%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-4,91%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-29,18%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-66,63%</t>
+          <t>-26,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-48,19%</t>
+          <t>-48,46%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 79,79</t>
+          <t>-40,03; 46,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,01; 63,57</t>
+          <t>-57,75; 21,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,21; 128,41</t>
+          <t>-100,0; 13,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-39,99; 52,42</t>
+          <t>-31,44; 70,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,72; 19,01</t>
+          <t>-43,18; 63,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 23,55</t>
+          <t>-80,94; 117,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,55; 42,34</t>
+          <t>-24,66; 44,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-41,03; 20,42</t>
+          <t>-39,5; 23,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-79,69; 21,27</t>
+          <t>-82,21; 14,36</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,64</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,39</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-4,63</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,26</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,86</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,64</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,3</t>
+          <t>-1,39</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,06</t>
+          <t>-3,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,57</t>
+          <t>-1,02; 4,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,57</t>
+          <t>-2,2; 3,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 4,45</t>
+          <t>-7,29; -1,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 4,36</t>
+          <t>-1,29; 4,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,88</t>
+          <t>-1,65; 3,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,16; -0,83</t>
+          <t>-5,57; 4,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,28</t>
+          <t>-0,33; 3,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,33</t>
+          <t>-1,25; 2,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,48; -0,09</t>
+          <t>-5,36; -0,15</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>19,67%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-55,32%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>14,73%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>10,05%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-16,52%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-51,45%</t>
+          <t>-16,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-36,23%</t>
+          <t>-38,0%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 49,02</t>
+          <t>-10,9; 60,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 50,21</t>
+          <t>-23,1; 44,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,45; 60,39</t>
+          <t>-77,6; -8,83</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 63,39</t>
+          <t>-13,43; 56,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 41,72</t>
+          <t>-16,95; 47,06</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-78,11; -10,5</t>
+          <t>-60,89; 60,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 44,3</t>
+          <t>-3,49; 41,77</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 30,19</t>
+          <t>-13,75; 31,83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-61,35; -1,46</t>
+          <t>-60,72; -2,07</t>
         </is>
       </c>
     </row>
